--- a/artfynd/A 52382-2025 artfynd.xlsx
+++ b/artfynd/A 52382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318239</v>
       </c>
       <c r="B2" t="n">
-        <v>93211</v>
+        <v>93214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52382-2025 artfynd.xlsx
+++ b/artfynd/A 52382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318239</v>
       </c>
       <c r="B2" t="n">
-        <v>93214</v>
+        <v>93220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52382-2025 artfynd.xlsx
+++ b/artfynd/A 52382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318239</v>
       </c>
       <c r="B2" t="n">
-        <v>93220</v>
+        <v>93230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52382-2025 artfynd.xlsx
+++ b/artfynd/A 52382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318239</v>
       </c>
       <c r="B2" t="n">
-        <v>93230</v>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
